--- a/leave_request_forms/005_request_for_leave_of_absence_form--leave_request_forms.xlsx
+++ b/leave_request_forms/005_request_for_leave_of_absence_form--leave_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>employer_name</t>
+          <t>company_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>Employee Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>employee_id</t>
+          <t>Employee ID</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>reason_for_leave</t>
+          <t>Reason for Leave</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>End Date</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>reason_for_absence</t>
+          <t>Reason for Absence</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>employee_returning_date</t>
+          <t>returning_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>employee_returning_date</t>
+          <t>Date of Returning to Work</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>manager_signature</t>
+          <t>Manager Signature</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>manager_name</t>
+          <t>Manager Name</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>manager_email</t>
+          <t>Manager Email</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>department_head_signature</t>
+          <t>Department Head Signature</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>department_head_name</t>
+          <t>Department Head Name</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>department_head_email</t>
+          <t>Department Head Email</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>employee_email</t>
+          <t>Employee Email</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>employee_phone</t>
+          <t>Employee Phone</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>manager_title</t>
+          <t>Manager Title</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>department_title</t>
+          <t>Department Title</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>employee_position</t>
+          <t>Employee Position</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,17 +975,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>employee_department</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Employee Department</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,85 +1003,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>employee_department</t>
+          <t>department_head_phone</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Employee Department</t>
+          <t>Department Head Phone</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>employee_department_name</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>employee_department_head_name</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>department_head_name</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>department_head_phone</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>department_head_phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1152,40 +1083,6 @@
         </is>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>department_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>department_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
